--- a/Focusinsight-reports/Disbursement/Pending-Sep-2026.xlsx
+++ b/Focusinsight-reports/Disbursement/Pending-Sep-2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Employee ID</t>
   </si>
@@ -25,10 +25,16 @@
     <t>Date</t>
   </si>
   <si>
-    <t>No records found.</t>
-  </si>
-  <si>
-    <t/>
+    <t>DEMO_EMP_EE</t>
+  </si>
+  <si>
+    <t>Demo Employee Electrical</t>
+  </si>
+  <si>
+    <t>Disbursement</t>
+  </si>
+  <si>
+    <t>30-Sep-2026</t>
   </si>
 </sst>
 </file>
@@ -445,10 +451,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
